--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.36074181419383</v>
+        <v>7.208620544806497</v>
       </c>
       <c r="D2" t="n">
-        <v>19.13789585078074</v>
+        <v>3.10990807575187</v>
       </c>
       <c r="E2" t="n">
-        <v>14.86299224401181</v>
+        <v>2.415236239651919</v>
       </c>
       <c r="F2" t="n">
-        <v>19.33646964882437</v>
+        <v>3.142176317933961</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.8212803310624</v>
+        <v>5.65845805379764</v>
       </c>
       <c r="D3" t="n">
-        <v>36.92554488167062</v>
+        <v>6.000401043271475</v>
       </c>
       <c r="E3" t="n">
-        <v>14.86299224401181</v>
+        <v>2.415236239651919</v>
       </c>
       <c r="F3" t="n">
-        <v>19.33646964882437</v>
+        <v>3.142176317933961</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>70.34448265310159</v>
+        <v>11.43097843112901</v>
       </c>
       <c r="D4" t="n">
-        <v>67.04598758752265</v>
+        <v>10.89497298297243</v>
       </c>
       <c r="E4" t="n">
-        <v>14.86299224401181</v>
+        <v>2.415236239651919</v>
       </c>
       <c r="F4" t="n">
-        <v>19.33646964882437</v>
+        <v>3.142176317933961</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.1519263098773</v>
+        <v>9.937188025355061</v>
       </c>
       <c r="D5" t="n">
-        <v>53.64064043254791</v>
+        <v>8.716604070289035</v>
       </c>
       <c r="E5" t="n">
-        <v>14.86299224401181</v>
+        <v>2.415236239651919</v>
       </c>
       <c r="F5" t="n">
-        <v>19.33646964882437</v>
+        <v>3.142176317933961</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>71.13594171944227</v>
+        <v>11.55959052940937</v>
       </c>
       <c r="D6" t="n">
-        <v>71.91527007204215</v>
+        <v>11.68623138670685</v>
       </c>
       <c r="E6" t="n">
-        <v>14.86299224401181</v>
+        <v>2.415236239651919</v>
       </c>
       <c r="F6" t="n">
-        <v>19.33646964882437</v>
+        <v>3.142176317933961</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>74.71594068992033</v>
+        <v>12.14134036211205</v>
       </c>
       <c r="D7" t="n">
-        <v>69.82010083268035</v>
+        <v>11.34576638531056</v>
       </c>
       <c r="E7" t="n">
-        <v>14.86299224401181</v>
+        <v>2.415236239651919</v>
       </c>
       <c r="F7" t="n">
-        <v>19.33646964882437</v>
+        <v>3.142176317933961</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
